--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-7B-Instruct-v0.3/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-7B-Instruct-v0.3/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E2">
         <v>37</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D3">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="G3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H3">
         <v>426</v>
